--- a/budget.xlsx
+++ b/budget.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\desk\google_drive\socdoneleft.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1934A732-F24F-4C26-8C04-E7D8BB1BCAEB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3BC38E-9D6D-4236-AF87-84F4B6FCE945}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="870" yWindow="-120" windowWidth="28050" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <definedName name="earningsrange">OFFSET(full!$D$2,0,0,COUNTA(full!$D:$D)-1)</definedName>
     <definedName name="runningrange">OFFSET(full!$E$2,0,0,COUNTA(full!$E:$E)-1)</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
